--- a/EX_GAS_Config/ProjectConfigTable/exgas_config/Datas/#exgas.mmc.xlsx
+++ b/EX_GAS_Config/ProjectConfigTable/exgas_config/Datas/#exgas.mmc.xlsx
@@ -15,7 +15,7 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="152511" fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -64,36 +64,48 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>##var</t>
   </si>
   <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Desc</t>
+  </si>
+  <si>
+    <t>MmcLogic</t>
+  </si>
+  <si>
+    <t>##type</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>##</t>
+  </si>
+  <si>
     <t>id</t>
   </si>
   <si>
-    <t>##type</t>
-  </si>
-  <si>
-    <t>int</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>##</t>
-  </si>
-  <si>
     <t>名字</t>
   </si>
   <si>
     <t>作用描述</t>
   </si>
   <si>
-    <r>
+    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <t>mmc修改器计算逻辑：支持多态，添加新</t>
     </r>
-    <r>
+    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
@@ -103,7 +115,7 @@
       </rPr>
       <t>Mmc</t>
     </r>
-    <r>
+    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
@@ -113,7 +125,7 @@
       </rPr>
       <t>Logic类型去__bean__中添加即可。暂定给了13个变量的预留位，不够的话就自己加长。</t>
     </r>
-    <phoneticPr fontId="0" type="noConversion"/>
+    <phoneticPr xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" fontId="0" type="noConversion"/>
   </si>
   <si>
     <t>模值x1</t>
@@ -137,31 +149,18 @@
     <t>test message3</t>
   </si>
   <si>
-    <t>MmcLogic</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
-    <t>ID</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
-    <t>Name</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
-    <t>Desc</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
-    <t>MmcLogic</t>
-    <phoneticPr fontId="0" type="noConversion"/>
+    <t>读取攻击力数值</t>
+  </si>
+  <si>
+    <t>MMCAttributeBased</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -175,21 +174,6 @@
       <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
     </font>
   </fonts>
   <fills count="2">
@@ -295,48 +279,50 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+  <cellXfs count="17">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="1" applyBorder="1" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="2" applyBorder="1" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="3" applyBorder="1" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="4" applyBorder="1" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="5" applyBorder="1" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="6" applyBorder="1" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="7" applyBorder="1" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="8" applyBorder="1" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="常规 2" xfId="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -617,250 +603,277 @@
   <dimension ref="A1:R26"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="16.21875" style="4" customWidth="1"/>
-    <col min="4" max="4" width="14.44140625" style="4" customWidth="1"/>
-    <col min="5" max="5" width="16.77734375" style="4" customWidth="1"/>
-    <col min="6" max="6" width="15" style="4" customWidth="1"/>
+    <col min="3" max="3" width="16.21875" customWidth="1" style="6"/>
+    <col min="4" max="4" width="14.44140625" customWidth="1" style="6"/>
+    <col min="5" max="5" width="16.77734375" customWidth="1" style="6"/>
+    <col min="6" max="6" width="15" customWidth="1" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
-      <c r="J1" s="7"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="7"/>
-      <c r="M1" s="7"/>
-      <c r="N1" s="7"/>
-      <c r="O1" s="7"/>
-      <c r="P1" s="7"/>
-      <c r="Q1" s="7"/>
-      <c r="R1" s="8"/>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="9"/>
+      <c r="N1" s="9"/>
+      <c r="O1" s="9"/>
+      <c r="P1" s="9"/>
+      <c r="Q1" s="9"/>
+      <c r="R1" s="10"/>
+    </row>
+    <row r="2">
       <c r="A2" s="1" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="10"/>
-      <c r="K2" s="10"/>
-      <c r="L2" s="10"/>
-      <c r="M2" s="10"/>
-      <c r="N2" s="10"/>
-      <c r="O2" s="10"/>
-      <c r="P2" s="10"/>
-      <c r="Q2" s="10"/>
-      <c r="R2" s="11"/>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="12"/>
+      <c r="J2" s="12"/>
+      <c r="K2" s="12"/>
+      <c r="L2" s="12"/>
+      <c r="M2" s="12"/>
+      <c r="N2" s="12"/>
+      <c r="O2" s="12"/>
+      <c r="P2" s="12"/>
+      <c r="Q2" s="12"/>
+      <c r="R2" s="13"/>
+    </row>
+    <row r="3">
       <c r="A3" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E3" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" s="13"/>
-      <c r="G3" s="13"/>
-      <c r="H3" s="13"/>
-      <c r="I3" s="13"/>
-      <c r="J3" s="13"/>
-      <c r="K3" s="13"/>
-      <c r="L3" s="13"/>
-      <c r="M3" s="13"/>
-      <c r="N3" s="13"/>
-      <c r="O3" s="13"/>
-      <c r="P3" s="13"/>
-      <c r="Q3" s="13"/>
-      <c r="R3" s="14"/>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+      <c r="E3" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="15"/>
+      <c r="G3" s="15"/>
+      <c r="H3" s="15"/>
+      <c r="I3" s="15"/>
+      <c r="J3" s="15"/>
+      <c r="K3" s="15"/>
+      <c r="L3" s="15"/>
+      <c r="M3" s="15"/>
+      <c r="N3" s="15"/>
+      <c r="O3" s="15"/>
+      <c r="P3" s="15"/>
+      <c r="Q3" s="15"/>
+      <c r="R3" s="16"/>
+    </row>
+    <row r="4">
       <c r="A4" s="1"/>
       <c r="B4" s="1">
         <v>1001</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" s="5">
+        <v>13</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" s="7">
         <v>1</v>
       </c>
-      <c r="G4" s="2">
+      <c r="G4" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="5">
       <c r="A5" s="1"/>
       <c r="B5" s="1">
         <v>1002</v>
       </c>
-      <c r="C5" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" s="5">
+      <c r="C5" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5" s="7">
         <v>3</v>
       </c>
-      <c r="G5" s="4">
+      <c r="G5" s="6">
         <v>0.5</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="B6" s="3">
+    <row r="6">
+      <c r="B6" s="5">
         <v>1003</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D6" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E6" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6" s="4">
+      <c r="F6" s="6">
         <v>1.5</v>
       </c>
-      <c r="G6" s="3">
+      <c r="G6" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="B7" s="5"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="7">
+      <c r="B7" s="7">
+        <v>2001</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F7" s="6">
+        <v>0</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0</v>
+      </c>
+      <c r="H7" s="3">
+        <v>0</v>
+      </c>
+      <c r="I7" s="3">
+        <v>0</v>
+      </c>
+      <c r="J7" s="3">
+        <v>1</v>
+      </c>
+      <c r="K7" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
       <c r="B8" s="1"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+    </row>
+    <row r="9">
       <c r="B9" s="1"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="B13" s="5"/>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+    </row>
+    <row r="10">
+      <c r="C10" s="7"/>
+      <c r="D10" s="7"/>
+    </row>
+    <row r="11">
+      <c r="C11" s="7"/>
+      <c r="D11" s="7"/>
+    </row>
+    <row r="12">
+      <c r="C12" s="7"/>
+      <c r="D12" s="7"/>
+    </row>
+    <row r="13">
+      <c r="B13" s="7"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+    </row>
+    <row r="14">
       <c r="B14" s="1"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="C14" s="7"/>
+      <c r="D14" s="7"/>
+    </row>
+    <row r="15">
       <c r="B15" s="1"/>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
+    </row>
+    <row r="16">
       <c r="B16" s="1"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-    </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+    </row>
+    <row r="17">
       <c r="B17" s="1"/>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
-    </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
+    </row>
+    <row r="18">
       <c r="B18" s="1"/>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
-    </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+    </row>
+    <row r="19">
       <c r="B19" s="1"/>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5"/>
-    </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C19" s="7"/>
+      <c r="D19" s="7"/>
+    </row>
+    <row r="20">
       <c r="B20" s="1"/>
-      <c r="C20" s="5"/>
-      <c r="D20" s="5"/>
-    </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B21" s="5"/>
-      <c r="C21" s="5"/>
-      <c r="D21" s="5"/>
-    </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C20" s="7"/>
+      <c r="D20" s="7"/>
+    </row>
+    <row r="21">
+      <c r="B21" s="7"/>
+      <c r="C21" s="7"/>
+      <c r="D21" s="7"/>
+    </row>
+    <row r="22">
       <c r="B22" s="1"/>
     </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="23">
       <c r="B23" s="1"/>
     </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B25" s="5"/>
-    </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="25">
+      <c r="B25" s="7"/>
+    </row>
+    <row r="26">
       <c r="B26" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells>
     <mergeCell ref="E1:R1"/>
     <mergeCell ref="E2:R2"/>
     <mergeCell ref="E3:R3"/>
@@ -868,6 +881,7 @@
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/EX_GAS_Config/ProjectConfigTable/exgas_config/Datas/#exgas.mmc.xlsx
+++ b/EX_GAS_Config/ProjectConfigTable/exgas_config/Datas/#exgas.mmc.xlsx
@@ -775,16 +775,16 @@
         <v>21</v>
       </c>
       <c r="F7" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H7" s="3">
         <v>0</v>
       </c>
       <c r="I7" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" s="3">
         <v>1</v>

--- a/EX_GAS_Config/ProjectConfigTable/exgas_config/Datas/#exgas.mmc.xlsx
+++ b/EX_GAS_Config/ProjectConfigTable/exgas_config/Datas/#exgas.mmc.xlsx
@@ -5,17 +5,17 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\MyRepo\gameplay-ability-system-for-unity\ProjectConfigTable\exgas_config\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\MyRepo\gameplay-ability-system-for-unity\EX_GAS_Config\ProjectConfigTable\exgas_config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAD40B25-D4C8-440A-8FC7-15DB4459D442}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AB4FDE6-8444-4656-BA35-7073886D0D4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="152511" fullCalcOnLoad="1"/>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="23">
   <si>
     <t>##var</t>
   </si>
@@ -102,10 +102,10 @@
     <t>作用描述</t>
   </si>
   <si>
-    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+    <r>
       <t>mmc修改器计算逻辑：支持多态，添加新</t>
     </r>
-    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+    <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
@@ -115,7 +115,7 @@
       </rPr>
       <t>Mmc</t>
     </r>
-    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+    <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
@@ -125,7 +125,7 @@
       </rPr>
       <t>Logic类型去__bean__中添加即可。暂定给了13个变量的预留位，不够的话就自己加长。</t>
     </r>
-    <phoneticPr xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" fontId="0" type="noConversion"/>
+    <phoneticPr fontId="0" type="noConversion"/>
   </si>
   <si>
     <t>模值x1</t>
@@ -153,14 +153,17 @@
   </si>
   <si>
     <t>MMCAttributeBased</t>
+  </si>
+  <si>
+    <t>ModMagnitudeCalculationBase</t>
+    <phoneticPr fontId="0" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -174,6 +177,21 @@
       <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="2">
@@ -279,50 +297,49 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
+  <cellXfs count="16">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="1" applyBorder="1" xfId="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="2" applyBorder="1" xfId="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="3" applyBorder="1" xfId="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="4" applyBorder="1" xfId="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="5" applyBorder="1" xfId="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="6" applyBorder="1" xfId="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="7" applyBorder="1" xfId="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="8" applyBorder="1" xfId="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="1"/>
+    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -603,13 +620,13 @@
   <dimension ref="A1:R26"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="16.21875" customWidth="1" style="6"/>
-    <col min="4" max="4" width="14.44140625" customWidth="1" style="6"/>
-    <col min="5" max="5" width="16.77734375" customWidth="1" style="6"/>
-    <col min="6" max="6" width="15" customWidth="1" style="6"/>
+    <col min="3" max="3" width="16.21875" style="5" customWidth="1"/>
+    <col min="4" max="4" width="14.44140625" style="5" customWidth="1"/>
+    <col min="5" max="5" width="16.77734375" style="5" customWidth="1"/>
+    <col min="6" max="6" width="15" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -622,24 +639,24 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
-      <c r="K1" s="9"/>
-      <c r="L1" s="9"/>
-      <c r="M1" s="9"/>
-      <c r="N1" s="9"/>
-      <c r="O1" s="9"/>
-      <c r="P1" s="9"/>
-      <c r="Q1" s="9"/>
-      <c r="R1" s="10"/>
-    </row>
-    <row r="2">
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
+      <c r="J1" s="8"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="8"/>
+      <c r="M1" s="8"/>
+      <c r="N1" s="8"/>
+      <c r="O1" s="8"/>
+      <c r="P1" s="8"/>
+      <c r="Q1" s="8"/>
+      <c r="R1" s="9"/>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -652,24 +669,24 @@
       <c r="D2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12"/>
-      <c r="H2" s="12"/>
-      <c r="I2" s="12"/>
-      <c r="J2" s="12"/>
-      <c r="K2" s="12"/>
-      <c r="L2" s="12"/>
-      <c r="M2" s="12"/>
-      <c r="N2" s="12"/>
-      <c r="O2" s="12"/>
-      <c r="P2" s="12"/>
-      <c r="Q2" s="12"/>
-      <c r="R2" s="13"/>
-    </row>
-    <row r="3">
+      <c r="E2" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2" s="11"/>
+      <c r="G2" s="11"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="11"/>
+      <c r="J2" s="11"/>
+      <c r="K2" s="11"/>
+      <c r="L2" s="11"/>
+      <c r="M2" s="11"/>
+      <c r="N2" s="11"/>
+      <c r="O2" s="11"/>
+      <c r="P2" s="11"/>
+      <c r="Q2" s="11"/>
+      <c r="R2" s="12"/>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
@@ -682,24 +699,24 @@
       <c r="D3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="14" t="s">
+      <c r="E3" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="15"/>
-      <c r="G3" s="15"/>
-      <c r="H3" s="15"/>
-      <c r="I3" s="15"/>
-      <c r="J3" s="15"/>
-      <c r="K3" s="15"/>
-      <c r="L3" s="15"/>
-      <c r="M3" s="15"/>
-      <c r="N3" s="15"/>
-      <c r="O3" s="15"/>
-      <c r="P3" s="15"/>
-      <c r="Q3" s="15"/>
-      <c r="R3" s="16"/>
-    </row>
-    <row r="4">
+      <c r="F3" s="14"/>
+      <c r="G3" s="14"/>
+      <c r="H3" s="14"/>
+      <c r="I3" s="14"/>
+      <c r="J3" s="14"/>
+      <c r="K3" s="14"/>
+      <c r="L3" s="14"/>
+      <c r="M3" s="14"/>
+      <c r="N3" s="14"/>
+      <c r="O3" s="14"/>
+      <c r="P3" s="14"/>
+      <c r="Q3" s="14"/>
+      <c r="R3" s="15"/>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="1">
         <v>1001</v>
@@ -707,173 +724,173 @@
       <c r="C4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="F4" s="7">
+      <c r="F4" s="6">
         <v>1</v>
       </c>
-      <c r="G4" s="4">
+      <c r="G4" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="1">
         <v>1002</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="E5" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="F5" s="7">
+      <c r="F5" s="6">
         <v>3</v>
       </c>
-      <c r="G5" s="6">
+      <c r="G5" s="5">
         <v>0.5</v>
       </c>
     </row>
-    <row r="6">
-      <c r="B6" s="5">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B6" s="4">
         <v>1003</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="F6" s="6">
+      <c r="F6" s="5">
         <v>1.5</v>
       </c>
-      <c r="G6" s="5">
+      <c r="G6" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="7">
-      <c r="B7" s="7">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B7" s="6">
         <v>2001</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="E7" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="F7" s="6">
+      <c r="F7" s="5">
         <v>1</v>
       </c>
-      <c r="G7" s="3">
+      <c r="G7" s="2">
         <v>4</v>
       </c>
-      <c r="H7" s="3">
+      <c r="H7" s="2">
         <v>0</v>
       </c>
-      <c r="I7" s="3">
+      <c r="I7" s="2">
         <v>1</v>
       </c>
-      <c r="J7" s="3">
+      <c r="J7" s="2">
         <v>1</v>
       </c>
-      <c r="K7" s="3">
+      <c r="K7" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B8" s="1"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-    </row>
-    <row r="9">
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B9" s="1"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-    </row>
-    <row r="10">
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-    </row>
-    <row r="11">
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-    </row>
-    <row r="12">
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-    </row>
-    <row r="13">
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-    </row>
-    <row r="14">
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B13" s="6"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B14" s="1"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-    </row>
-    <row r="15">
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B15" s="1"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-    </row>
-    <row r="16">
+      <c r="C15" s="6"/>
+      <c r="D15" s="6"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B16" s="1"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-    </row>
-    <row r="17">
+      <c r="C16" s="6"/>
+      <c r="D16" s="6"/>
+    </row>
+    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B17" s="1"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-    </row>
-    <row r="18">
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+    </row>
+    <row r="18" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B18" s="1"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-    </row>
-    <row r="19">
+      <c r="C18" s="6"/>
+      <c r="D18" s="6"/>
+    </row>
+    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B19" s="1"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-    </row>
-    <row r="20">
+      <c r="C19" s="6"/>
+      <c r="D19" s="6"/>
+    </row>
+    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B20" s="1"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-    </row>
-    <row r="21">
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-    </row>
-    <row r="22">
+      <c r="C20" s="6"/>
+      <c r="D20" s="6"/>
+    </row>
+    <row r="21" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B21" s="6"/>
+      <c r="C21" s="6"/>
+      <c r="D21" s="6"/>
+    </row>
+    <row r="22" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B22" s="1"/>
     </row>
-    <row r="23">
+    <row r="23" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B23" s="1"/>
     </row>
-    <row r="25">
-      <c r="B25" s="7"/>
-    </row>
-    <row r="26">
+    <row r="25" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B25" s="6"/>
+    </row>
+    <row r="26" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B26" s="1"/>
     </row>
   </sheetData>
-  <mergeCells>
+  <mergeCells count="3">
     <mergeCell ref="E1:R1"/>
     <mergeCell ref="E2:R2"/>
     <mergeCell ref="E3:R3"/>
@@ -881,7 +898,6 @@
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>